--- a/artifacts/mobile/assets/dialogues.xlsx
+++ b/artifacts/mobile/assets/dialogues.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://volvogroup-my.sharepoint.com/personal/xiaolin_li_volvo_com/Documents/Desktop/往期存档/模型/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_AC77C320F2A8FC67DE60022B0894ABFBA02CF1E2" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FE440122-A767-42D8-9D55-CDC67353B23A}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="11_1547213E98E9F8570D666F497DE60D26B0828655" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFE14490-FCFD-4554-BD36-EA5CA9091E56}"/>
   <bookViews>
-    <workbookView xWindow="10650" yWindow="6015" windowWidth="22980" windowHeight="13635" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5970" yWindow="6060" windowWidth="27690" windowHeight="13635" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="角色对话" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="556" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="371">
   <si>
     <t>说明/触发条件</t>
   </si>
@@ -1120,19 +1120,19 @@
     <t>啊……缝合好了……里面感觉怪怪的……少了一截……</t>
   </si>
   <si>
-    <t>啊……！肚脐……被贯通了！今后手指都能全部插进来了！</t>
-  </si>
-  <si>
-    <t>肚脐穿了，好奇怪的感觉,肠子不会露出来吧？</t>
-  </si>
-  <si>
-    <t>嗯啊……！通了肚子里面……有风进来了，肠子在颤抖。</t>
-  </si>
-  <si>
-    <t>肚脐感觉好奇怪凉飕飕的，肚子里面也感觉不一样了呢</t>
-  </si>
-  <si>
-    <t>肚脐变成这样，洗澡水会灌进肚子里吗？！</t>
+    <t>啊！肚脐被贯通了！</t>
+  </si>
+  <si>
+    <t>呜…肚脐穿了……好奇怪的感觉，现在手指都能全部插进来了。</t>
+  </si>
+  <si>
+    <t>嗯啊！通了！肚子里面有风进来了…好敏感</t>
+  </si>
+  <si>
+    <t>肚脐变成这个样子，洗澡时水会不会灌进肚子里？</t>
+  </si>
+  <si>
+    <t>肠子不会露出来吧？</t>
   </si>
 </sst>
 </file>
@@ -1510,13 +1510,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:G77"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="60.875" customWidth="1"/>
     <col min="2" max="7" width="40.875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1539,7 +1539,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -1562,7 +1562,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>12</v>
       </c>
@@ -1585,7 +1585,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>16</v>
       </c>
@@ -1608,7 +1608,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>20</v>
       </c>
@@ -1631,7 +1631,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -1654,7 +1654,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>28</v>
       </c>
@@ -1677,7 +1677,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>32</v>
       </c>
@@ -1700,7 +1700,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>36</v>
       </c>
@@ -1723,7 +1723,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>40</v>
       </c>
@@ -1746,7 +1746,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>44</v>
       </c>
@@ -1769,7 +1769,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>48</v>
       </c>
@@ -1792,7 +1792,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>52</v>
       </c>
@@ -1815,7 +1815,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>56</v>
       </c>
@@ -1838,7 +1838,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>60</v>
       </c>
@@ -1861,7 +1861,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>64</v>
       </c>
@@ -1884,7 +1884,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>68</v>
       </c>
@@ -1907,7 +1907,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>73</v>
       </c>
@@ -1930,7 +1930,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>78</v>
       </c>
@@ -1953,7 +1953,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>83</v>
       </c>
@@ -1976,7 +1976,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>88</v>
       </c>
@@ -1999,7 +1999,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>92</v>
       </c>
@@ -2022,7 +2022,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>97</v>
       </c>
@@ -2045,7 +2045,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>102</v>
       </c>
@@ -2068,7 +2068,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>107</v>
       </c>
@@ -2091,7 +2091,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>111</v>
       </c>
@@ -2114,7 +2114,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>115</v>
       </c>
@@ -2137,7 +2137,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>119</v>
       </c>
@@ -2160,7 +2160,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>125</v>
       </c>
@@ -2183,7 +2183,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>132</v>
       </c>
@@ -2206,7 +2206,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>139</v>
       </c>
@@ -2229,7 +2229,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>145</v>
       </c>
@@ -2252,7 +2252,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>150</v>
       </c>
@@ -2275,7 +2275,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>156</v>
       </c>
@@ -2298,7 +2298,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="35" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>162</v>
       </c>
@@ -2321,7 +2321,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="36" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>167</v>
       </c>
@@ -2344,7 +2344,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="37" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>172</v>
       </c>
@@ -2367,7 +2367,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="38" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>178</v>
       </c>
@@ -2390,7 +2390,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>184</v>
       </c>
@@ -2413,7 +2413,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="40" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>189</v>
       </c>
@@ -2436,7 +2436,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="41" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>193</v>
       </c>
@@ -2459,7 +2459,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="42" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>198</v>
       </c>
@@ -2482,7 +2482,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="43" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>203</v>
       </c>
@@ -2505,7 +2505,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="44" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>209</v>
       </c>
@@ -2528,7 +2528,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="45" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>215</v>
       </c>
@@ -2551,7 +2551,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="46" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>220</v>
       </c>
@@ -2574,7 +2574,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="47" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>225</v>
       </c>
@@ -2597,7 +2597,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="48" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>230</v>
       </c>
@@ -2620,7 +2620,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="49" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>235</v>
       </c>
@@ -2643,7 +2643,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>240</v>
       </c>
@@ -2666,7 +2666,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>245</v>
       </c>
@@ -2689,7 +2689,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="52" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>250</v>
       </c>
@@ -2712,7 +2712,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="53" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>251</v>
       </c>
@@ -2735,7 +2735,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>256</v>
       </c>
@@ -2758,7 +2758,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>261</v>
       </c>
@@ -2781,7 +2781,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>266</v>
       </c>
@@ -2804,7 +2804,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>271</v>
       </c>
@@ -2827,7 +2827,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>276</v>
       </c>
@@ -2850,7 +2850,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>281</v>
       </c>
@@ -2873,7 +2873,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>286</v>
       </c>
@@ -2896,7 +2896,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>290</v>
       </c>
@@ -2919,7 +2919,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>294</v>
       </c>
@@ -2942,7 +2942,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>298</v>
       </c>
@@ -2965,7 +2965,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>302</v>
       </c>
@@ -2988,7 +2988,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>306</v>
       </c>
@@ -3011,7 +3011,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>310</v>
       </c>
@@ -3034,7 +3034,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>314</v>
       </c>
@@ -3057,7 +3057,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>318</v>
       </c>
@@ -3080,7 +3080,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>322</v>
       </c>
@@ -3103,7 +3103,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>326</v>
       </c>
@@ -3126,7 +3126,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>333</v>
       </c>
@@ -3149,7 +3149,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>339</v>
       </c>
@@ -3172,7 +3172,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="73" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>345</v>
       </c>
@@ -3195,7 +3195,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="74" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>350</v>
       </c>
@@ -3218,7 +3218,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="75" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>354</v>
       </c>
@@ -3241,7 +3241,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="76" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>358</v>
       </c>
@@ -3264,7 +3264,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="77" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>362</v>
       </c>
@@ -3290,13 +3290,13 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:G51 A53:G77 A52 G52" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:G51 A53:G77 G52" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
-  <clbl:label id="{19540963-e559-4020-8a90-fe8a502c2801}" enabled="1" method="Standard" siteId="{f25493ae-1c98-41d7-8a33-0be75f5fe603}" contentBits="0" removed="0"/>
+  <clbl:label id="{19540963-e559-4020-8a90-fe8a502c2801}" enabled="1" method="Standard" siteId="{f25493ae-1c98-41d7-8a33-0be75f5fe603}" removed="0"/>
 </clbl:labelList>
 </file>
--- a/artifacts/mobile/assets/dialogues.xlsx
+++ b/artifacts/mobile/assets/dialogues.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://volvogroup-my.sharepoint.com/personal/xiaolin_li_volvo_com/Documents/Desktop/往期存档/模型/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="7" documentId="11_1547213E98E9F8570D666F497DE60D26B0828655" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FFE14490-FCFD-4554-BD36-EA5CA9091E56}"/>
+  <xr:revisionPtr revIDLastSave="103" documentId="11_1547213E98E9F8570D666F497DE60D26B0828655" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{07609D6F-D222-445E-A4DE-3A2301241664}"/>
   <bookViews>
-    <workbookView xWindow="5970" yWindow="6060" windowWidth="27690" windowHeight="13635" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3552" yWindow="132" windowWidth="19488" windowHeight="13548" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="角色对话" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="371">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="640" uniqueCount="391">
   <si>
     <t>说明/触发条件</t>
   </si>
@@ -49,27 +49,12 @@
     <t>……</t>
   </si>
   <si>
-    <t>嗯……</t>
-  </si>
-  <si>
-    <t>……（深呼吸）</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
     <t>[low_pressure] 腹腔内压较低（灌入液体/气体较少），轻微胀满感</t>
   </si>
   <si>
-    <t>呜……肚子感觉满满的……</t>
-  </si>
-  <si>
-    <t>嗯……里面有点胀……</t>
-  </si>
-  <si>
-    <t>啊……里面被填满了……</t>
-  </si>
-  <si>
     <t>[medium_pressure] 腹腔内压中等，明显撑胀感</t>
   </si>
   <si>
@@ -85,39 +70,12 @@
     <t>[high_pressure] 腹腔内压高，剧烈撑痛感，接近危险</t>
   </si>
   <si>
-    <t>不、不行……太撑了……要爆开了……！</t>
-  </si>
-  <si>
-    <t>呜啊……里面压力太大了……！</t>
-  </si>
-  <si>
-    <t>啊啊……好痛……撑太满了……！</t>
-  </si>
-  <si>
     <t>[critical_pressure] 腹腔内压极高，即将穿孔，危急状态</t>
   </si>
   <si>
-    <t>不行了不行了……！撑爆了……！</t>
-  </si>
-  <si>
-    <t>啊啊啊……！要炸开了……！</t>
-  </si>
-  <si>
-    <t>撑……撑太满了……要爆了……！</t>
-  </si>
-  <si>
     <t>[explosion] 因压力过大导致肠管穿孔/爆裂</t>
   </si>
   <si>
-    <t>啊啊啊……！穿孔了……！</t>
-  </si>
-  <si>
-    <t>呜……肠子……穿了个洞……</t>
-  </si>
-  <si>
-    <t>不行……破了……好痛……</t>
-  </si>
-  <si>
     <t>[pain_low] 轻微疼痛刺激（轻度操作、轻触等）</t>
   </si>
   <si>
@@ -133,15 +91,6 @@
     <t>[pain_high] 强烈疼痛刺激（深刺、强压、穿刺等）</t>
   </si>
   <si>
-    <t>啊啊……好痛……！求求你……</t>
-  </si>
-  <si>
-    <t>不行……！太痛了……！</t>
-  </si>
-  <si>
-    <t>呜呜……疼死了……！</t>
-  </si>
-  <si>
     <t>[pleasure_low] 轻微快感（初级刺激，身体有奇怪感觉）</t>
   </si>
   <si>
@@ -157,12 +106,6 @@
     <t>[pleasure_medium] 中等快感（持续刺激，身体发热）</t>
   </si>
   <si>
-    <t>嗯啊……不要……感觉好奇怪……</t>
-  </si>
-  <si>
-    <t>哈……怎么……感觉这么好……</t>
-  </si>
-  <si>
     <t>呜……身体在发热……</t>
   </si>
   <si>
@@ -172,12 +115,6 @@
     <t>不……不行了……！好舒服……！</t>
   </si>
   <si>
-    <t>哈啊……！要不行了……！</t>
-  </si>
-  <si>
-    <t>啊……快感……太强了……！</t>
-  </si>
-  <si>
     <t>[grab] 用手或工具抓住/拉扯肠管节点</t>
   </si>
   <si>
@@ -187,39 +124,15 @@
     <t>呜……别拽……！</t>
   </si>
   <si>
-    <t>嗯……好奇怪的感觉……</t>
-  </si>
-  <si>
     <t>[vibrate] 振动蛋工具启动，肠道内持续振动刺激</t>
   </si>
   <si>
-    <t>嗯啊……！里面在抖……！</t>
-  </si>
-  <si>
-    <t>呜……振动……太强了……！</t>
-  </si>
-  <si>
-    <t>哈……什么感觉……！</t>
-  </si>
-  <si>
     <t>[needle_pierce] 针头刺穿肠管操作</t>
   </si>
   <si>
-    <t>啊！被刺到了……！</t>
-  </si>
-  <si>
-    <t>呜……刺进来了……好怪……</t>
-  </si>
-  <si>
-    <t>嗯……肠子被刺穿了……</t>
-  </si>
-  <si>
     <t>[enema_start] 灌肠器开始注液，液体开始进入肠道</t>
   </si>
   <si>
-    <t>呜……在灌什么进来……</t>
-  </si>
-  <si>
     <t>啊……里面有液体进来了……</t>
   </si>
   <si>
@@ -229,33 +142,12 @@
     <t>[enema_large_shallow] 灌肠管进入大肠浅段（肛门刚插入）</t>
   </si>
   <si>
-    <t>嗯……有什么……进来了……</t>
-  </si>
-  <si>
     <t>呜……肛门里……有东西插进来……</t>
   </si>
   <si>
-    <t>啊……什么……往里钻……</t>
-  </si>
-  <si>
-    <t>嗯……感觉到了……有什么东西……</t>
-  </si>
-  <si>
     <t>[enema_large_medium] 灌肠管进入大肠中段</t>
   </si>
   <si>
-    <t>呜……进来好多了……！里面被撑开了……</t>
-  </si>
-  <si>
-    <t>啊……越来越深……停下来……</t>
-  </si>
-  <si>
-    <t>嗯啊……插得好深……往里走了……</t>
-  </si>
-  <si>
-    <t>不要……再往里进了……！</t>
-  </si>
-  <si>
     <t>[enema_large_deep] 灌肠管进入大肠深段（接近回盲部）</t>
   </si>
   <si>
@@ -274,24 +166,12 @@
     <t>[enema_enter_small] 灌肠管穿过回盲瓣进入小肠</t>
   </si>
   <si>
-    <t>啊啊……！进……进小肠了……！太深了……！</t>
-  </si>
-  <si>
-    <t>呜……不行……越来越深……！感觉穿过去了……！</t>
-  </si>
-  <si>
-    <t>嗯啊……！液体……液体进到小肠里了……！好奇怪……！</t>
-  </si>
-  <si>
     <t>不……不要再进了……！已经进到小肠了……！</t>
   </si>
   <si>
     <t>[enema_small_shallow] 灌肠管在小肠浅段运动</t>
   </si>
   <si>
-    <t>嗯……进到小肠了……好深……</t>
-  </si>
-  <si>
     <t>呜……小肠里……有什么在动……</t>
   </si>
   <si>
@@ -301,27 +181,12 @@
     <t>[enema_small_medium] 灌肠管在小肠中段推进</t>
   </si>
   <si>
-    <t>不行……！太深了……！小肠里……！</t>
-  </si>
-  <si>
-    <t>啊啊……小肠被撑开了……好难受……</t>
-  </si>
-  <si>
     <t>呜啊……越来越深……！小肠……受不了……</t>
   </si>
   <si>
-    <t>嗯……里面好热……小肠被填满了……</t>
-  </si>
-  <si>
     <t>[enema_small_deep] 灌肠管到达小肠深段（空回肠交界附近）</t>
   </si>
   <si>
-    <t>啊啊啊……！太深了太深了……！小肠最深处……！</t>
-  </si>
-  <si>
-    <t>不行了……！进到小肠最里面了……！好怪……！</t>
-  </si>
-  <si>
     <t>呜啊啊……！小肠……撑得要爆了……！太深了……！</t>
   </si>
   <si>
@@ -331,30 +196,18 @@
     <t>[enema_retract] 灌肠管开始向外退出</t>
   </si>
   <si>
-    <t>呜……慢慢……出来了……</t>
-  </si>
-  <si>
     <t>嗯……在往外拔……</t>
   </si>
   <si>
     <t>啊……出来了一点……</t>
   </si>
   <si>
-    <t>呜……终于……往外退了……</t>
-  </si>
-  <si>
     <t>[intestine_break] 肠管因过度拉扯或穿孔导致断裂</t>
   </si>
   <si>
     <t>啊啊啊……！肠子断了……！</t>
   </si>
   <si>
-    <t>不行了……！里面断了什么……！</t>
-  </si>
-  <si>
-    <t>呜啊……！撕裂感……！</t>
-  </si>
-  <si>
     <t>[rupture] 肠壁穿孔（非爆炸性，工具刺破或压力穿孔）</t>
   </si>
   <si>
@@ -364,39 +217,18 @@
     <t>不行……里面破了一个洞……</t>
   </si>
   <si>
-    <t>啊……肠壁……破了……</t>
-  </si>
-  <si>
     <t>[electric] 电击工具通用触发（不分肠段，触电瞬间反应）</t>
   </si>
   <si>
-    <t>啊！！电……电到了……！</t>
-  </si>
-  <si>
-    <t>呜啊……！麻麻的……！</t>
-  </si>
-  <si>
-    <t>不行……！被电到了……！</t>
-  </si>
-  <si>
     <t>[electric_low] 低电压电击，轻微麻感（通用，不分大小肠）</t>
   </si>
   <si>
-    <t>嗯……？有点麻……</t>
-  </si>
-  <si>
-    <t>啊……微微的……电流……</t>
-  </si>
-  <si>
     <t>呜……有什么在动……怪怪的……</t>
   </si>
   <si>
     <t>嗯……肚子里有点麻麻的……</t>
   </si>
   <si>
-    <t>哈……这是……电的感觉……？</t>
-  </si>
-  <si>
     <t>[electric_medium] 中电压电击，明显抽搐（通用，不分大小肠）</t>
   </si>
   <si>
@@ -1133,6 +965,234 @@
   </si>
   <si>
     <t>肠子不会露出来吧？</t>
+  </si>
+  <si>
+    <t>嗯…好无聊，对我的肚子做点什么吧！什么都可以哦~</t>
+  </si>
+  <si>
+    <t>（深呼吸）</t>
+  </si>
+  <si>
+    <t>别一直盯着这里看，我好害羞~</t>
+  </si>
+  <si>
+    <t>我的肚子很漂亮吧，肚脐也很深哦~</t>
+  </si>
+  <si>
+    <t>你要对我做什么？</t>
+  </si>
+  <si>
+    <t>肚子里面好像有点胀……</t>
+  </si>
+  <si>
+    <t>呜…肚子里有点奇怪的感觉……</t>
+  </si>
+  <si>
+    <t>嗯…我还能够接受。</t>
+  </si>
+  <si>
+    <t>不、不行！快停下来！肠子……要爆开了……！</t>
+  </si>
+  <si>
+    <t>呜啊……肠子里面压力太大了……！</t>
+  </si>
+  <si>
+    <t>啊啊……好痛……肚子撑太满了……！</t>
+  </si>
+  <si>
+    <t>不行了不行了……！肠子要撑爆了……！</t>
+  </si>
+  <si>
+    <t>啊啊啊……！要炸开了…救命！</t>
+  </si>
+  <si>
+    <t>已经超过极限了，肠子要破了！</t>
+  </si>
+  <si>
+    <t>啊啊啊……！肚子好痛，好像里面有什么被撑破了！</t>
+  </si>
+  <si>
+    <t>呜……肠子被撑爆了……现在肯定肠穿孔了</t>
+  </si>
+  <si>
+    <t>糟糕！肠子被撑破了，完蛋了！</t>
+  </si>
+  <si>
+    <t>啊啊，肠子被撑破了！如果不做肠道修补手术我会死掉的！</t>
+  </si>
+  <si>
+    <t>啊啊……好痛……！求求你别这样…</t>
+  </si>
+  <si>
+    <t>不行！太痛了！</t>
+  </si>
+  <si>
+    <t>呜呜……疼死了！</t>
+  </si>
+  <si>
+    <t>我喜欢这种感觉，你可以更进一步……</t>
+  </si>
+  <si>
+    <t>嗯啊……肚子感觉好奇怪……</t>
+  </si>
+  <si>
+    <t>哈…怎么…感觉有点爽？！</t>
+  </si>
+  <si>
+    <t>太爽了，不要停下来！</t>
+  </si>
+  <si>
+    <t>啊……快感……太强烈了……！</t>
+  </si>
+  <si>
+    <t>太刺激了，我要去了！</t>
+  </si>
+  <si>
+    <t>肠子被抓住的感觉实在太奇怪了！</t>
+  </si>
+  <si>
+    <t>可以让我摸摸吗？</t>
+  </si>
+  <si>
+    <t>呕，肚子深处好像有什么被抓住了。</t>
+  </si>
+  <si>
+    <t>嗯啊……！肠子里面在抖……！</t>
+  </si>
+  <si>
+    <t>呜…振动太强了…就在肠子里面！</t>
+  </si>
+  <si>
+    <t>震动好舒服，肠子动起来了！</t>
+  </si>
+  <si>
+    <t>哈…肠子被振动器震的好酥麻…！</t>
+  </si>
+  <si>
+    <t>啊！刺到肠子了！</t>
+  </si>
+  <si>
+    <t>真的刺进来了……好怪……</t>
+  </si>
+  <si>
+    <t>肠子被刺穿了！</t>
+  </si>
+  <si>
+    <t>这样会肠穿孔的，温柔一点！</t>
+  </si>
+  <si>
+    <t>呜…好像有什么东西灌进来了。</t>
+  </si>
+  <si>
+    <t>嗯……有什么……进来了</t>
+  </si>
+  <si>
+    <t>啊……什么东西在往里钻！？</t>
+  </si>
+  <si>
+    <t>嗯……感觉到了……后穴有什么东西插进来了。</t>
+  </si>
+  <si>
+    <t>哇，插进来好多……！里面都被撑开了！</t>
+  </si>
+  <si>
+    <t>啊……越来越深…快停下来！</t>
+  </si>
+  <si>
+    <t>嗯啊……插得好深……往里面走了。</t>
+  </si>
+  <si>
+    <t>不要…再往里进了……！</t>
+  </si>
+  <si>
+    <t>插到底了！肚子都被顶起来了！</t>
+  </si>
+  <si>
+    <t>啊啊……！怎么可能？！进……进小肠了里面了……！太深了……！</t>
+  </si>
+  <si>
+    <t>怎么会？！感觉穿过去了……！难道，小肠？！</t>
+  </si>
+  <si>
+    <t>嗯啊……！进到小肠里面了……！好奇怪……！</t>
+  </si>
+  <si>
+    <t>这种感觉，一定是进到小肠里面了，这怎么可能？骗人的吧？</t>
+  </si>
+  <si>
+    <t>嗯…真的进到小肠里面了……太深了。</t>
+  </si>
+  <si>
+    <t>不要…再往里进了…小肠太细会戳破的！</t>
+  </si>
+  <si>
+    <t>感觉在小肠里面摩擦。</t>
+  </si>
+  <si>
+    <t>小肠里…还在往里面钻…！</t>
+  </si>
+  <si>
+    <t>呕…小肠被撑开了……好难受……</t>
+  </si>
+  <si>
+    <t>嗯……里面好紧……小肠被填满了……</t>
+  </si>
+  <si>
+    <t>啊啊啊……！太深了太深了……！小肠最深处…！</t>
+  </si>
+  <si>
+    <t>进到小肠最里面了…好像在肚脐下面…！好奇怪……！</t>
+  </si>
+  <si>
+    <t>已经进到肚脐下面了，我知道这种感觉！</t>
+  </si>
+  <si>
+    <t>呜…终于要出来了……</t>
+  </si>
+  <si>
+    <t>呜……终于要结束了吗？</t>
+  </si>
+  <si>
+    <t>肚子！肚子里面好像有什么被扯断了！</t>
+  </si>
+  <si>
+    <t>难道是肠子断了？…好强的撕裂感……！</t>
+  </si>
+  <si>
+    <t>啊啊啊啊，我的肠子被弄断了！</t>
+  </si>
+  <si>
+    <t>哇啊，肠子断了！快把肠子接起来，我会死掉的！</t>
+  </si>
+  <si>
+    <t>糟糕！肠子断了!这下只能做手术了，┭┮﹏┭┮</t>
+  </si>
+  <si>
+    <t>啊……肠壁……破了？</t>
+  </si>
+  <si>
+    <t>肠子好痛，被戳破了！</t>
+  </si>
+  <si>
+    <t>呜呜，肠子破了，这下必须要做手术了。</t>
+  </si>
+  <si>
+    <t>呜啊……！肚子里面麻麻的……！</t>
+  </si>
+  <si>
+    <t>啊！！电……肠子被电到了……！好刺激！</t>
+  </si>
+  <si>
+    <t>被电到了，好刺激！</t>
+  </si>
+  <si>
+    <t>嗯……？有点麻麻</t>
+  </si>
+  <si>
+    <t>啊……微微的……电流感……</t>
+  </si>
+  <si>
+    <t>哈……这就是被电的感觉吗……？</t>
   </si>
 </sst>
 </file>
@@ -1185,6 +1245,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1547,1750 +1611,1744 @@
         <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>315</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>316</v>
       </c>
       <c r="E2" t="s">
-        <v>11</v>
+        <v>317</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>318</v>
       </c>
       <c r="G2" t="s">
-        <v>11</v>
+        <v>319</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B3" t="s">
-        <v>13</v>
+        <v>321</v>
       </c>
       <c r="C3" t="s">
-        <v>14</v>
+        <v>320</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>322</v>
       </c>
       <c r="E3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G3" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C4" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="D4" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>323</v>
       </c>
       <c r="C5" t="s">
-        <v>22</v>
+        <v>324</v>
       </c>
       <c r="D5" t="s">
-        <v>23</v>
+        <v>325</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G5" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="B6" t="s">
-        <v>25</v>
+        <v>326</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>327</v>
       </c>
       <c r="D6" t="s">
-        <v>27</v>
-      </c>
-      <c r="E6" t="s">
-        <v>11</v>
+        <v>328</v>
       </c>
       <c r="F6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G6" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>329</v>
       </c>
       <c r="C7" t="s">
-        <v>30</v>
+        <v>330</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>331</v>
       </c>
       <c r="E7" t="s">
-        <v>11</v>
+        <v>332</v>
       </c>
       <c r="F7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G7" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>32</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>20</v>
       </c>
       <c r="D8" t="s">
-        <v>35</v>
+        <v>21</v>
       </c>
       <c r="E8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="B9" t="s">
-        <v>37</v>
+        <v>333</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>334</v>
       </c>
       <c r="D9" t="s">
-        <v>39</v>
+        <v>335</v>
       </c>
       <c r="E9" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F9" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G9" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>40</v>
+        <v>23</v>
       </c>
       <c r="B10" t="s">
-        <v>41</v>
+        <v>24</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>25</v>
       </c>
       <c r="D10" t="s">
-        <v>43</v>
+        <v>26</v>
       </c>
       <c r="E10" t="s">
-        <v>11</v>
+        <v>336</v>
       </c>
       <c r="F10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>44</v>
+        <v>27</v>
       </c>
       <c r="B11" t="s">
-        <v>45</v>
+        <v>337</v>
       </c>
       <c r="C11" t="s">
-        <v>46</v>
+        <v>338</v>
       </c>
       <c r="D11" t="s">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="E11" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F11" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G11" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>48</v>
+        <v>29</v>
       </c>
       <c r="B12" t="s">
-        <v>49</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>50</v>
+        <v>339</v>
       </c>
       <c r="D12" t="s">
-        <v>51</v>
+        <v>340</v>
       </c>
       <c r="E12" t="s">
-        <v>11</v>
+        <v>341</v>
       </c>
       <c r="F12" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G12" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="B13" t="s">
-        <v>53</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
       <c r="D13" t="s">
-        <v>55</v>
+        <v>342</v>
       </c>
       <c r="E13" t="s">
-        <v>11</v>
+        <v>343</v>
       </c>
       <c r="F13" t="s">
-        <v>11</v>
+        <v>344</v>
       </c>
       <c r="G13" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>56</v>
+        <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>57</v>
+        <v>345</v>
       </c>
       <c r="C14" t="s">
-        <v>58</v>
+        <v>346</v>
       </c>
       <c r="D14" t="s">
-        <v>59</v>
+        <v>348</v>
       </c>
       <c r="E14" t="s">
-        <v>11</v>
-      </c>
-      <c r="F14" t="s">
-        <v>11</v>
+        <v>347</v>
       </c>
       <c r="G14" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>61</v>
+        <v>349</v>
       </c>
       <c r="C15" t="s">
-        <v>62</v>
+        <v>350</v>
       </c>
       <c r="D15" t="s">
-        <v>63</v>
+        <v>351</v>
       </c>
       <c r="E15" t="s">
-        <v>11</v>
+        <v>352</v>
       </c>
       <c r="F15" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G15" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>64</v>
+        <v>36</v>
       </c>
       <c r="B16" t="s">
-        <v>65</v>
+        <v>353</v>
       </c>
       <c r="C16" t="s">
-        <v>66</v>
+        <v>37</v>
       </c>
       <c r="D16" t="s">
-        <v>67</v>
+        <v>38</v>
       </c>
       <c r="E16" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G16" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="B17" t="s">
-        <v>69</v>
+        <v>354</v>
       </c>
       <c r="C17" t="s">
-        <v>70</v>
+        <v>40</v>
       </c>
       <c r="D17" t="s">
-        <v>71</v>
+        <v>355</v>
       </c>
       <c r="E17" t="s">
-        <v>72</v>
+        <v>356</v>
       </c>
       <c r="F17" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G17" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>73</v>
+        <v>41</v>
       </c>
       <c r="B18" t="s">
-        <v>74</v>
+        <v>357</v>
       </c>
       <c r="C18" t="s">
-        <v>75</v>
+        <v>358</v>
       </c>
       <c r="D18" t="s">
-        <v>76</v>
+        <v>359</v>
       </c>
       <c r="E18" t="s">
-        <v>77</v>
+        <v>360</v>
       </c>
       <c r="F18" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G18" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>78</v>
+        <v>42</v>
       </c>
       <c r="B19" t="s">
-        <v>79</v>
+        <v>43</v>
       </c>
       <c r="C19" t="s">
-        <v>80</v>
+        <v>44</v>
       </c>
       <c r="D19" t="s">
-        <v>81</v>
+        <v>45</v>
       </c>
       <c r="E19" t="s">
-        <v>82</v>
+        <v>46</v>
       </c>
       <c r="F19" t="s">
-        <v>11</v>
+        <v>361</v>
       </c>
       <c r="G19" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>83</v>
+        <v>47</v>
       </c>
       <c r="B20" t="s">
-        <v>84</v>
+        <v>362</v>
       </c>
       <c r="C20" t="s">
-        <v>85</v>
+        <v>363</v>
       </c>
       <c r="D20" t="s">
-        <v>86</v>
+        <v>364</v>
       </c>
       <c r="E20" t="s">
-        <v>87</v>
+        <v>48</v>
       </c>
       <c r="F20" t="s">
-        <v>11</v>
+        <v>365</v>
       </c>
       <c r="G20" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>88</v>
+        <v>49</v>
       </c>
       <c r="B21" t="s">
-        <v>89</v>
+        <v>366</v>
       </c>
       <c r="C21" t="s">
-        <v>90</v>
+        <v>50</v>
       </c>
       <c r="D21" t="s">
-        <v>91</v>
+        <v>51</v>
       </c>
       <c r="E21" t="s">
-        <v>11</v>
+        <v>367</v>
       </c>
       <c r="F21" t="s">
-        <v>11</v>
+        <v>368</v>
       </c>
       <c r="G21" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>92</v>
+        <v>52</v>
       </c>
       <c r="B22" t="s">
-        <v>93</v>
+        <v>369</v>
       </c>
       <c r="C22" t="s">
-        <v>94</v>
+        <v>370</v>
       </c>
       <c r="D22" t="s">
-        <v>95</v>
+        <v>53</v>
       </c>
       <c r="E22" t="s">
-        <v>96</v>
+        <v>371</v>
       </c>
       <c r="F22" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G22" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>97</v>
+        <v>54</v>
       </c>
       <c r="B23" t="s">
-        <v>98</v>
+        <v>372</v>
       </c>
       <c r="C23" t="s">
-        <v>99</v>
+        <v>373</v>
       </c>
       <c r="D23" t="s">
-        <v>100</v>
+        <v>55</v>
       </c>
       <c r="E23" t="s">
-        <v>101</v>
+        <v>56</v>
       </c>
       <c r="F23" t="s">
-        <v>11</v>
+        <v>374</v>
       </c>
       <c r="G23" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>102</v>
+        <v>57</v>
       </c>
       <c r="B24" t="s">
-        <v>103</v>
+        <v>375</v>
       </c>
       <c r="C24" t="s">
-        <v>104</v>
+        <v>58</v>
       </c>
       <c r="D24" t="s">
-        <v>105</v>
+        <v>59</v>
       </c>
       <c r="E24" t="s">
-        <v>106</v>
+        <v>376</v>
       </c>
       <c r="F24" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G24" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>107</v>
+        <v>60</v>
       </c>
       <c r="B25" t="s">
-        <v>108</v>
+        <v>61</v>
       </c>
       <c r="C25" t="s">
-        <v>109</v>
+        <v>377</v>
       </c>
       <c r="D25" t="s">
-        <v>110</v>
+        <v>378</v>
       </c>
       <c r="E25" t="s">
-        <v>11</v>
+        <v>379</v>
       </c>
       <c r="F25" t="s">
-        <v>11</v>
+        <v>380</v>
       </c>
       <c r="G25" t="s">
-        <v>11</v>
+        <v>381</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>111</v>
+        <v>62</v>
       </c>
       <c r="B26" t="s">
-        <v>112</v>
+        <v>63</v>
       </c>
       <c r="C26" t="s">
-        <v>113</v>
+        <v>64</v>
       </c>
       <c r="D26" t="s">
-        <v>114</v>
+        <v>382</v>
       </c>
       <c r="E26" t="s">
-        <v>11</v>
+        <v>383</v>
       </c>
       <c r="F26" t="s">
-        <v>11</v>
+        <v>384</v>
       </c>
       <c r="G26" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>115</v>
+        <v>65</v>
       </c>
       <c r="B27" t="s">
-        <v>116</v>
+        <v>386</v>
       </c>
       <c r="C27" t="s">
-        <v>117</v>
+        <v>385</v>
       </c>
       <c r="D27" t="s">
-        <v>118</v>
+        <v>387</v>
       </c>
       <c r="E27" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F27" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G27" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>119</v>
+        <v>66</v>
       </c>
       <c r="B28" t="s">
-        <v>120</v>
+        <v>388</v>
       </c>
       <c r="C28" t="s">
-        <v>121</v>
+        <v>389</v>
       </c>
       <c r="D28" t="s">
-        <v>122</v>
+        <v>67</v>
       </c>
       <c r="E28" t="s">
-        <v>123</v>
+        <v>68</v>
       </c>
       <c r="F28" t="s">
-        <v>124</v>
+        <v>390</v>
       </c>
       <c r="G28" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>125</v>
+        <v>69</v>
       </c>
       <c r="B29" t="s">
-        <v>126</v>
+        <v>70</v>
       </c>
       <c r="C29" t="s">
-        <v>127</v>
+        <v>71</v>
       </c>
       <c r="D29" t="s">
-        <v>128</v>
+        <v>72</v>
       </c>
       <c r="E29" t="s">
-        <v>129</v>
+        <v>73</v>
       </c>
       <c r="F29" t="s">
-        <v>130</v>
+        <v>74</v>
       </c>
       <c r="G29" t="s">
-        <v>131</v>
+        <v>75</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>132</v>
+        <v>76</v>
       </c>
       <c r="B30" t="s">
-        <v>133</v>
+        <v>77</v>
       </c>
       <c r="C30" t="s">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="D30" t="s">
-        <v>135</v>
+        <v>79</v>
       </c>
       <c r="E30" t="s">
-        <v>136</v>
+        <v>80</v>
       </c>
       <c r="F30" t="s">
-        <v>137</v>
+        <v>81</v>
       </c>
       <c r="G30" t="s">
-        <v>138</v>
+        <v>82</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>139</v>
+        <v>83</v>
       </c>
       <c r="B31" t="s">
-        <v>140</v>
+        <v>84</v>
       </c>
       <c r="C31" t="s">
-        <v>141</v>
+        <v>85</v>
       </c>
       <c r="D31" t="s">
-        <v>142</v>
+        <v>86</v>
       </c>
       <c r="E31" t="s">
-        <v>143</v>
+        <v>87</v>
       </c>
       <c r="F31" t="s">
-        <v>144</v>
+        <v>88</v>
       </c>
       <c r="G31" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>145</v>
+        <v>89</v>
       </c>
       <c r="B32" t="s">
-        <v>146</v>
+        <v>90</v>
       </c>
       <c r="C32" t="s">
-        <v>147</v>
+        <v>91</v>
       </c>
       <c r="D32" t="s">
-        <v>148</v>
+        <v>92</v>
       </c>
       <c r="E32" t="s">
-        <v>149</v>
+        <v>93</v>
       </c>
       <c r="F32" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G32" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>150</v>
+        <v>94</v>
       </c>
       <c r="B33" t="s">
-        <v>151</v>
+        <v>95</v>
       </c>
       <c r="C33" t="s">
-        <v>152</v>
+        <v>96</v>
       </c>
       <c r="D33" t="s">
-        <v>153</v>
+        <v>97</v>
       </c>
       <c r="E33" t="s">
-        <v>154</v>
+        <v>98</v>
       </c>
       <c r="F33" t="s">
-        <v>155</v>
+        <v>99</v>
       </c>
       <c r="G33" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>156</v>
+        <v>100</v>
       </c>
       <c r="B34" t="s">
-        <v>157</v>
+        <v>101</v>
       </c>
       <c r="C34" t="s">
-        <v>158</v>
+        <v>102</v>
       </c>
       <c r="D34" t="s">
-        <v>159</v>
+        <v>103</v>
       </c>
       <c r="E34" t="s">
-        <v>160</v>
+        <v>104</v>
       </c>
       <c r="F34" t="s">
-        <v>161</v>
+        <v>105</v>
       </c>
       <c r="G34" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>162</v>
+        <v>106</v>
       </c>
       <c r="B35" t="s">
-        <v>163</v>
+        <v>107</v>
       </c>
       <c r="C35" t="s">
-        <v>164</v>
+        <v>108</v>
       </c>
       <c r="D35" t="s">
-        <v>165</v>
+        <v>109</v>
       </c>
       <c r="E35" t="s">
-        <v>166</v>
+        <v>110</v>
       </c>
       <c r="F35" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G35" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>167</v>
+        <v>111</v>
       </c>
       <c r="B36" t="s">
-        <v>168</v>
+        <v>112</v>
       </c>
       <c r="C36" t="s">
-        <v>169</v>
+        <v>113</v>
       </c>
       <c r="D36" t="s">
-        <v>170</v>
+        <v>114</v>
       </c>
       <c r="E36" t="s">
-        <v>171</v>
+        <v>115</v>
       </c>
       <c r="F36" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G36" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>172</v>
+        <v>116</v>
       </c>
       <c r="B37" t="s">
-        <v>173</v>
+        <v>117</v>
       </c>
       <c r="C37" t="s">
-        <v>174</v>
+        <v>118</v>
       </c>
       <c r="D37" t="s">
-        <v>175</v>
+        <v>119</v>
       </c>
       <c r="E37" t="s">
-        <v>176</v>
+        <v>120</v>
       </c>
       <c r="F37" t="s">
-        <v>177</v>
+        <v>121</v>
       </c>
       <c r="G37" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>178</v>
+        <v>122</v>
       </c>
       <c r="B38" t="s">
-        <v>179</v>
+        <v>123</v>
       </c>
       <c r="C38" t="s">
-        <v>180</v>
+        <v>124</v>
       </c>
       <c r="D38" t="s">
-        <v>181</v>
+        <v>125</v>
       </c>
       <c r="E38" t="s">
-        <v>182</v>
+        <v>126</v>
       </c>
       <c r="F38" t="s">
-        <v>183</v>
+        <v>127</v>
       </c>
       <c r="G38" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>184</v>
+        <v>128</v>
       </c>
       <c r="B39" t="s">
-        <v>185</v>
+        <v>129</v>
       </c>
       <c r="C39" t="s">
-        <v>186</v>
+        <v>130</v>
       </c>
       <c r="D39" t="s">
-        <v>187</v>
+        <v>131</v>
       </c>
       <c r="E39" t="s">
-        <v>188</v>
+        <v>132</v>
       </c>
       <c r="F39" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G39" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>189</v>
+        <v>133</v>
       </c>
       <c r="B40" t="s">
-        <v>190</v>
+        <v>134</v>
       </c>
       <c r="C40" t="s">
-        <v>191</v>
+        <v>135</v>
       </c>
       <c r="D40" t="s">
-        <v>192</v>
+        <v>136</v>
       </c>
       <c r="E40" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F40" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G40" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>193</v>
+        <v>137</v>
       </c>
       <c r="B41" t="s">
-        <v>194</v>
+        <v>138</v>
       </c>
       <c r="C41" t="s">
-        <v>195</v>
+        <v>139</v>
       </c>
       <c r="D41" t="s">
-        <v>196</v>
+        <v>140</v>
       </c>
       <c r="E41" t="s">
-        <v>197</v>
+        <v>141</v>
       </c>
       <c r="F41" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G41" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>198</v>
+        <v>142</v>
       </c>
       <c r="B42" t="s">
-        <v>199</v>
+        <v>143</v>
       </c>
       <c r="C42" t="s">
-        <v>200</v>
+        <v>144</v>
       </c>
       <c r="D42" t="s">
-        <v>201</v>
+        <v>145</v>
       </c>
       <c r="E42" t="s">
-        <v>202</v>
+        <v>146</v>
       </c>
       <c r="F42" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G42" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>203</v>
+        <v>147</v>
       </c>
       <c r="B43" t="s">
-        <v>204</v>
+        <v>148</v>
       </c>
       <c r="C43" t="s">
-        <v>205</v>
+        <v>149</v>
       </c>
       <c r="D43" t="s">
-        <v>206</v>
+        <v>150</v>
       </c>
       <c r="E43" t="s">
-        <v>207</v>
+        <v>151</v>
       </c>
       <c r="F43" t="s">
-        <v>208</v>
+        <v>152</v>
       </c>
       <c r="G43" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>209</v>
+        <v>153</v>
       </c>
       <c r="B44" t="s">
-        <v>210</v>
+        <v>154</v>
       </c>
       <c r="C44" t="s">
-        <v>211</v>
+        <v>155</v>
       </c>
       <c r="D44" t="s">
-        <v>212</v>
+        <v>156</v>
       </c>
       <c r="E44" t="s">
-        <v>213</v>
+        <v>157</v>
       </c>
       <c r="F44" t="s">
-        <v>214</v>
+        <v>158</v>
       </c>
       <c r="G44" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>215</v>
+        <v>159</v>
       </c>
       <c r="B45" t="s">
-        <v>216</v>
+        <v>160</v>
       </c>
       <c r="C45" t="s">
-        <v>217</v>
+        <v>161</v>
       </c>
       <c r="D45" t="s">
-        <v>218</v>
+        <v>162</v>
       </c>
       <c r="E45" t="s">
-        <v>219</v>
+        <v>163</v>
       </c>
       <c r="F45" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G45" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>220</v>
+        <v>164</v>
       </c>
       <c r="B46" t="s">
-        <v>221</v>
+        <v>165</v>
       </c>
       <c r="C46" t="s">
-        <v>222</v>
+        <v>166</v>
       </c>
       <c r="D46" t="s">
-        <v>223</v>
+        <v>167</v>
       </c>
       <c r="E46" t="s">
-        <v>224</v>
+        <v>168</v>
       </c>
       <c r="F46" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G46" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>225</v>
+        <v>169</v>
       </c>
       <c r="B47" t="s">
-        <v>226</v>
+        <v>170</v>
       </c>
       <c r="C47" t="s">
-        <v>227</v>
+        <v>171</v>
       </c>
       <c r="D47" t="s">
-        <v>228</v>
+        <v>172</v>
       </c>
       <c r="E47" t="s">
-        <v>229</v>
+        <v>173</v>
       </c>
       <c r="F47" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G47" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>230</v>
+        <v>174</v>
       </c>
       <c r="B48" t="s">
-        <v>231</v>
+        <v>175</v>
       </c>
       <c r="C48" t="s">
-        <v>232</v>
+        <v>176</v>
       </c>
       <c r="D48" t="s">
-        <v>233</v>
+        <v>177</v>
       </c>
       <c r="E48" t="s">
-        <v>234</v>
+        <v>178</v>
       </c>
       <c r="F48" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G48" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>235</v>
+        <v>179</v>
       </c>
       <c r="B49" t="s">
-        <v>236</v>
+        <v>180</v>
       </c>
       <c r="C49" t="s">
-        <v>237</v>
+        <v>181</v>
       </c>
       <c r="D49" t="s">
-        <v>238</v>
+        <v>182</v>
       </c>
       <c r="E49" t="s">
-        <v>239</v>
+        <v>183</v>
       </c>
       <c r="F49" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G49" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>240</v>
+        <v>184</v>
       </c>
       <c r="B50" t="s">
-        <v>241</v>
+        <v>185</v>
       </c>
       <c r="C50" t="s">
-        <v>242</v>
+        <v>186</v>
       </c>
       <c r="D50" t="s">
-        <v>243</v>
+        <v>187</v>
       </c>
       <c r="E50" t="s">
-        <v>244</v>
+        <v>188</v>
       </c>
       <c r="F50" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G50" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>245</v>
+        <v>189</v>
       </c>
       <c r="B51" t="s">
-        <v>246</v>
+        <v>190</v>
       </c>
       <c r="C51" t="s">
-        <v>247</v>
+        <v>191</v>
       </c>
       <c r="D51" t="s">
-        <v>248</v>
+        <v>192</v>
       </c>
       <c r="E51" t="s">
-        <v>249</v>
+        <v>193</v>
       </c>
       <c r="F51" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G51" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>250</v>
+        <v>194</v>
       </c>
       <c r="B52" t="s">
-        <v>366</v>
+        <v>310</v>
       </c>
       <c r="C52" t="s">
-        <v>367</v>
+        <v>311</v>
       </c>
       <c r="D52" t="s">
-        <v>368</v>
+        <v>312</v>
       </c>
       <c r="E52" t="s">
-        <v>369</v>
+        <v>313</v>
       </c>
       <c r="F52" t="s">
-        <v>370</v>
+        <v>314</v>
       </c>
       <c r="G52" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>251</v>
+        <v>195</v>
       </c>
       <c r="B53" t="s">
-        <v>252</v>
+        <v>196</v>
       </c>
       <c r="C53" t="s">
-        <v>253</v>
+        <v>197</v>
       </c>
       <c r="D53" t="s">
-        <v>254</v>
+        <v>198</v>
       </c>
       <c r="E53" t="s">
-        <v>255</v>
+        <v>199</v>
       </c>
       <c r="F53" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G53" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>256</v>
+        <v>200</v>
       </c>
       <c r="B54" t="s">
-        <v>257</v>
+        <v>201</v>
       </c>
       <c r="C54" t="s">
-        <v>258</v>
+        <v>202</v>
       </c>
       <c r="D54" t="s">
-        <v>259</v>
+        <v>203</v>
       </c>
       <c r="E54" t="s">
-        <v>260</v>
+        <v>204</v>
       </c>
       <c r="F54" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G54" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>261</v>
+        <v>205</v>
       </c>
       <c r="B55" t="s">
-        <v>262</v>
+        <v>206</v>
       </c>
       <c r="C55" t="s">
-        <v>263</v>
+        <v>207</v>
       </c>
       <c r="D55" t="s">
-        <v>264</v>
+        <v>208</v>
       </c>
       <c r="E55" t="s">
-        <v>265</v>
+        <v>209</v>
       </c>
       <c r="F55" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G55" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>266</v>
+        <v>210</v>
       </c>
       <c r="B56" t="s">
-        <v>267</v>
+        <v>211</v>
       </c>
       <c r="C56" t="s">
-        <v>268</v>
+        <v>212</v>
       </c>
       <c r="D56" t="s">
-        <v>269</v>
+        <v>213</v>
       </c>
       <c r="E56" t="s">
-        <v>270</v>
+        <v>214</v>
       </c>
       <c r="F56" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G56" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>271</v>
+        <v>215</v>
       </c>
       <c r="B57" t="s">
-        <v>272</v>
+        <v>216</v>
       </c>
       <c r="C57" t="s">
-        <v>273</v>
+        <v>217</v>
       </c>
       <c r="D57" t="s">
-        <v>274</v>
+        <v>218</v>
       </c>
       <c r="E57" t="s">
-        <v>275</v>
+        <v>219</v>
       </c>
       <c r="F57" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G57" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>276</v>
+        <v>220</v>
       </c>
       <c r="B58" t="s">
-        <v>277</v>
+        <v>221</v>
       </c>
       <c r="C58" t="s">
-        <v>278</v>
+        <v>222</v>
       </c>
       <c r="D58" t="s">
-        <v>279</v>
+        <v>223</v>
       </c>
       <c r="E58" t="s">
-        <v>280</v>
+        <v>224</v>
       </c>
       <c r="F58" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G58" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>281</v>
+        <v>225</v>
       </c>
       <c r="B59" t="s">
-        <v>282</v>
+        <v>226</v>
       </c>
       <c r="C59" t="s">
-        <v>283</v>
+        <v>227</v>
       </c>
       <c r="D59" t="s">
-        <v>284</v>
+        <v>228</v>
       </c>
       <c r="E59" t="s">
-        <v>285</v>
+        <v>229</v>
       </c>
       <c r="F59" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G59" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>286</v>
+        <v>230</v>
       </c>
       <c r="B60" t="s">
-        <v>287</v>
+        <v>231</v>
       </c>
       <c r="C60" t="s">
-        <v>288</v>
+        <v>232</v>
       </c>
       <c r="D60" t="s">
-        <v>289</v>
+        <v>233</v>
       </c>
       <c r="E60" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F60" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G60" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>290</v>
+        <v>234</v>
       </c>
       <c r="B61" t="s">
-        <v>291</v>
+        <v>235</v>
       </c>
       <c r="C61" t="s">
-        <v>292</v>
+        <v>236</v>
       </c>
       <c r="D61" t="s">
-        <v>293</v>
+        <v>237</v>
       </c>
       <c r="E61" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F61" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G61" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>294</v>
+        <v>238</v>
       </c>
       <c r="B62" t="s">
-        <v>295</v>
+        <v>239</v>
       </c>
       <c r="C62" t="s">
-        <v>296</v>
+        <v>240</v>
       </c>
       <c r="D62" t="s">
-        <v>297</v>
+        <v>241</v>
       </c>
       <c r="E62" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F62" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G62" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>298</v>
+        <v>242</v>
       </c>
       <c r="B63" t="s">
-        <v>299</v>
+        <v>243</v>
       </c>
       <c r="C63" t="s">
-        <v>300</v>
+        <v>244</v>
       </c>
       <c r="D63" t="s">
-        <v>301</v>
+        <v>245</v>
       </c>
       <c r="E63" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F63" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G63" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>302</v>
+        <v>246</v>
       </c>
       <c r="B64" t="s">
-        <v>303</v>
+        <v>247</v>
       </c>
       <c r="C64" t="s">
-        <v>304</v>
+        <v>248</v>
       </c>
       <c r="D64" t="s">
-        <v>305</v>
+        <v>249</v>
       </c>
       <c r="E64" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F64" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G64" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>306</v>
+        <v>250</v>
       </c>
       <c r="B65" t="s">
-        <v>307</v>
+        <v>251</v>
       </c>
       <c r="C65" t="s">
-        <v>308</v>
+        <v>252</v>
       </c>
       <c r="D65" t="s">
-        <v>309</v>
+        <v>253</v>
       </c>
       <c r="E65" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F65" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G65" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>310</v>
+        <v>254</v>
       </c>
       <c r="B66" t="s">
-        <v>311</v>
+        <v>255</v>
       </c>
       <c r="C66" t="s">
-        <v>312</v>
+        <v>256</v>
       </c>
       <c r="D66" t="s">
-        <v>313</v>
+        <v>257</v>
       </c>
       <c r="E66" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F66" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G66" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>314</v>
+        <v>258</v>
       </c>
       <c r="B67" t="s">
-        <v>315</v>
+        <v>259</v>
       </c>
       <c r="C67" t="s">
-        <v>316</v>
+        <v>260</v>
       </c>
       <c r="D67" t="s">
-        <v>317</v>
+        <v>261</v>
       </c>
       <c r="E67" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F67" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G67" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>318</v>
+        <v>262</v>
       </c>
       <c r="B68" t="s">
-        <v>319</v>
+        <v>263</v>
       </c>
       <c r="C68" t="s">
-        <v>320</v>
+        <v>264</v>
       </c>
       <c r="D68" t="s">
-        <v>321</v>
+        <v>265</v>
       </c>
       <c r="E68" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F68" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G68" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>322</v>
+        <v>266</v>
       </c>
       <c r="B69" t="s">
-        <v>323</v>
+        <v>267</v>
       </c>
       <c r="C69" t="s">
-        <v>324</v>
+        <v>268</v>
       </c>
       <c r="D69" t="s">
-        <v>325</v>
+        <v>269</v>
       </c>
       <c r="E69" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F69" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G69" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>326</v>
+        <v>270</v>
       </c>
       <c r="B70" t="s">
-        <v>327</v>
+        <v>271</v>
       </c>
       <c r="C70" t="s">
-        <v>328</v>
+        <v>272</v>
       </c>
       <c r="D70" t="s">
-        <v>329</v>
+        <v>273</v>
       </c>
       <c r="E70" t="s">
-        <v>330</v>
+        <v>274</v>
       </c>
       <c r="F70" t="s">
-        <v>331</v>
+        <v>275</v>
       </c>
       <c r="G70" t="s">
-        <v>332</v>
+        <v>276</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>333</v>
+        <v>277</v>
       </c>
       <c r="B71" t="s">
-        <v>334</v>
+        <v>278</v>
       </c>
       <c r="C71" t="s">
-        <v>335</v>
+        <v>279</v>
       </c>
       <c r="D71" t="s">
-        <v>336</v>
+        <v>280</v>
       </c>
       <c r="E71" t="s">
-        <v>337</v>
+        <v>281</v>
       </c>
       <c r="F71" t="s">
-        <v>338</v>
+        <v>282</v>
       </c>
       <c r="G71" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>339</v>
+        <v>283</v>
       </c>
       <c r="B72" t="s">
-        <v>340</v>
+        <v>284</v>
       </c>
       <c r="C72" t="s">
-        <v>341</v>
+        <v>285</v>
       </c>
       <c r="D72" t="s">
-        <v>342</v>
+        <v>286</v>
       </c>
       <c r="E72" t="s">
-        <v>343</v>
+        <v>287</v>
       </c>
       <c r="F72" t="s">
-        <v>344</v>
+        <v>288</v>
       </c>
       <c r="G72" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>345</v>
+        <v>289</v>
       </c>
       <c r="B73" t="s">
-        <v>346</v>
+        <v>290</v>
       </c>
       <c r="C73" t="s">
-        <v>347</v>
+        <v>291</v>
       </c>
       <c r="D73" t="s">
-        <v>348</v>
+        <v>292</v>
       </c>
       <c r="E73" t="s">
-        <v>349</v>
+        <v>293</v>
       </c>
       <c r="F73" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G73" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>350</v>
+        <v>294</v>
       </c>
       <c r="B74" t="s">
-        <v>351</v>
+        <v>295</v>
       </c>
       <c r="C74" t="s">
-        <v>352</v>
+        <v>296</v>
       </c>
       <c r="D74" t="s">
-        <v>353</v>
+        <v>297</v>
       </c>
       <c r="E74" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F74" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G74" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>354</v>
+        <v>298</v>
       </c>
       <c r="B75" t="s">
-        <v>355</v>
+        <v>299</v>
       </c>
       <c r="C75" t="s">
-        <v>356</v>
+        <v>300</v>
       </c>
       <c r="D75" t="s">
-        <v>357</v>
+        <v>301</v>
       </c>
       <c r="E75" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F75" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G75" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>358</v>
+        <v>302</v>
       </c>
       <c r="B76" t="s">
-        <v>359</v>
+        <v>303</v>
       </c>
       <c r="C76" t="s">
-        <v>360</v>
+        <v>304</v>
       </c>
       <c r="D76" t="s">
-        <v>361</v>
+        <v>305</v>
       </c>
       <c r="E76" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F76" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G76" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>362</v>
+        <v>306</v>
       </c>
       <c r="B77" t="s">
-        <v>363</v>
+        <v>307</v>
       </c>
       <c r="C77" t="s">
-        <v>364</v>
+        <v>308</v>
       </c>
       <c r="D77" t="s">
-        <v>365</v>
+        <v>309</v>
       </c>
       <c r="E77" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F77" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G77" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:G51 A53:G77 G52" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:G1 A53:G77 G52 A4:G4 A2:B2 A3 E3:G3 A8:G8 A5 E5:G5 A6 F6:G6 A7 F7:G7 A29:G51 A9 E9:G9 A10:C10 F10:G10 A11 D11:G11 A12 F12:G12 A13:C13 G13 A14 G14 A15 F15:G15 A16 C16:G16 A17 C17 F17:G17 A18 F18:G18 A19:D19 G19 A20 G20 A21 G21 A22 F22:G22 A23 G23 A24 C24 F24:G24 A25:B25 A26:C26 G26 A27 E27:G27 A28 D28:E28 G28" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
